--- a/Result/checksun_type/交易撮(媒)合.xlsx
+++ b/Result/checksun_type/交易撮(媒)合.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>74.24</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>75.94</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>78.82</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>75.94</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>78.81999999999999</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>709.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>378.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>378.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>754.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>1063.24</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>1063.24</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-65.36342660409002</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>709</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>709.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>74.06</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>76.03</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>78.98</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>76.03</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>78.98</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>384.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>555.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>555.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>684.0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>1078.44</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>1078.44</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-81.31309747373018</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>384</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>384.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>74.1</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>76.2</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>79.17</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>79.17</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>189.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>1003.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>1003.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>665.3</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>1085.84</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>1085.84</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-66.3728738062972</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>189</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>189.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>74.74</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>76.39</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>79.33</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>76.39</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>79.33</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>461.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>997.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>997</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>732.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>1111.82</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>1111.82</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-21.76638021688211</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>461</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>461.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>75.54</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>76.6</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>79.51</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>79.51000000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>149.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>1109.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>1109.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>833.5</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>1227.54</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>1227.54</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>13.59169563288503</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>149</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>76.02000000000001</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>76.72</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>79.69</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>76.72</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>79.69</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>1595.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>1130.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>1130.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>970.4</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>1231.96</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>1231.96</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>97.04638628852092</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>1595</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>1595.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>76.67999999999999</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>76.82</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>79.87</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>76.81999999999999</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>79.87</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>2623.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>812.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>812.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>872.2</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>1215.96</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>1215.96</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>57.87285914341066</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>2623</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>2623.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>77.26000000000002</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>76.88</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>80.05</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>76.88</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>80.05</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>157.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>327.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>327.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>724.2</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>1165.2</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>1165.2</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-110.2990674618686</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>157</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>157.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>77.3</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>76.79</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>80.17</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>76.79000000000001</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>80.17</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>1025.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>468.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>468.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>767.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>1165.84</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>1165.84</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-82.39113877434352</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>1025</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>1025.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>77.14000000000001</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>76.71</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>80.29</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>76.70999999999999</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>80.29000000000001</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>252.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>557.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>557.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>750.8</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>1161.16</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>1161.16</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-132.5801285502242</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>252</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>77.0</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>76.63</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>80.44</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>76.63</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>80.44</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>810.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>810.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>743.3</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>1172.74</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>1172.74</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-116.7222522104029</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>5</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>172.0</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>173.25</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>175.69</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>173.25</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>175.69</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>7733.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>4697.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>4697</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>5851.9</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>6254.16</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>6254.16</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-213.6578208302117</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>7733</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>7733.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>171.7</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>173.4</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>175.78</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>173.4</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>175.78</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>2499.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>3843.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>3843.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>5698.5</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>6350.88</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>6350.88</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-501.9615915926261</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>2499</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>2499.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>171.7</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>173.58</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>175.93</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>173.58</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>175.93</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>2106.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>4604.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>4604.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>6779.7</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>6392.4</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>6392.4</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-335.1112072677661</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>2106</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2106.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>171.8</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>173.75</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>176.05</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>173.75</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>176.05</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>7079.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>5289.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>5289.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>6948.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>6520.9</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>6520.9</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-42.67811511554646</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>7079</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>7079.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>172.1</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>173.98</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>176.23</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>173.98</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>176.23</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>4068.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>6534.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>6534.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>6326.4</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>6493.66</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>6493.66</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-156.2137650725354</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>4068</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>4068.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>172.4</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>174.18</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>176.39</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>174.18</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>176.39</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>3465.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>7006.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>7006.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>6196.7</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>6501.12</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>6501.12</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>9.778655170071033</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>3465</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>3465.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>173.0</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>174.4</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>176.56</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>174.4</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>176.56</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>6303.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>7553.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>7553.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>6534.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>6580.28</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>6580.28</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>311.1685892605783</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>6303</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>6303.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>173.0</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>174.52</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>176.72</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>174.52</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>176.72</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>5533.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>8955.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>8955.200000000001</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>6264.0</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>6656.86</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>6656.86</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>426.5410454877101</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>5533</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>5533.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>173.3</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>174.7</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>176.84</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>174.7</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>176.84</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>13304.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>8608.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>8608.200000000001</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>6084.4</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>6721.58</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>6721.58</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>658.6252313304803</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>13304</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>13304.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>173.7</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>174.88</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>176.96</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>174.88</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>176.96</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>6429.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>6118.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>6118.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>5270.3</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>6705.14</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>6705.14</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>134.0445957012062</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>6429</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>6429.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>173.9</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>175.02</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>177.08</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>175.02</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>177.08</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>6199.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>5386.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>5386.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>5295.9</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>6752.54</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>6752.54</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>116.4635235272017</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>6199</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>6199.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>29.77</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>31.24</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>32.69</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>31.24</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>32.69</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>6196.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>4029.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>4029.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>8268.9</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>12441.16</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>12441.16</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-1352.524974521401</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>6196</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>6196.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>29.63</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>31.39</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>32.81</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>32.81</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>3353.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>3338.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>3338.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>8346.5</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>12570.58</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>12570.58</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-1503.965968060494</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>3353</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>3353.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>29.55</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>31.62</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>32.94</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>32.94</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>2843.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>7106.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>7106.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>9387.3</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>12890.06</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>12890.06</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-1361.990031399894</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>2843</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>2843.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>29.67</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>31.88</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>33.08</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>33.08</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>4344.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>7733.6</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>7733.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>11140.1</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>13691.0</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>13691</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-1055.881906477613</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>4344</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>4344.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>30.01</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>32.09</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>33.26</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>33.26</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>3412.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>11323.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>11323.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>11014.9</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>14102.64</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>14102.64</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-741.6959456430086</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>3412</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>3412.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>30.46</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>32.32</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>33.43</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>33.43</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>2739.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>12508.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>12508.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>11371.0</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>14833.28</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>14833.28</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-166.5125749634681</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>2739</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>2739.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>30.71</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>32.49</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>33.57</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>33.57</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>22193.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>13354.8</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>13354.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>11675.7</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>15081.48</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>15081.48</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>733.2319751131417</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>22193</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>22193.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>31.01</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>33.71</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>33.71</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>5980.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>11668.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>11668.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>10614.9</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>14838.68</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>14838.68</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-91.96266674574144</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>5980</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>5980.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>31.33</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>32.76</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>33.84</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>33.84</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>22293.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>14546.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>14546.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>11359.4</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>15090.18</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>15090.18</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>469.5793686967736</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>22293</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>22293.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>31.59</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>32.86</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>33.94</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>32.86</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>33.94</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>9336.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>10706.4</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>10706.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>9618.2</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>15611.26</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>15611.26</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-492.8098438388042</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>9336</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>9336.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>31.7</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>32.9</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>34.05</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>34.05</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>6972.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>10233.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>10233.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>9540.5</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>16690.46</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>16690.46</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-461.8012244668171</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>6972</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>6972.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>127.5</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>129.78</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>129.14</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>129.78</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>129.14</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>7694.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>2769.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>2769.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>3408.2</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>3151.24</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>3151.24</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>191.1864117596488</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>7694</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>7694.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>127.5</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>130.0</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>129.16</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>129.16</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>1977.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>1337.8</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>1337.8</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>2929.9</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>3100.54</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>3100.54</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-256.6590140188805</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>1977</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>1977.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>127.6</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>130.2</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>129.19</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>130.2</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>129.19</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>1670.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>1332.2</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>1332.2</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>2922.9</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>3137.1</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>3137.1</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-274.7360860589615</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>1670</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>1670.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>127.7</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>130.38</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>129.21</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>130.38</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>129.21</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>942.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>1283.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>1283.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>2957.5</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>3293.8</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>3293.8</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-257.8556144712575</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>942</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>942.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>127.7</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>130.45</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>129.23</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>130.45</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>129.23</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>1563.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>3955.8</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>3955.8</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>2967.7</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>3329.8</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>3329.8</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-146.5315259719923</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>1563</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>1563.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>128.7</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>130.48</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>129.26</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>130.48</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>129.26</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>537.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>4047.2</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>4047.2</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>2845.3</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>3349.3</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>3349.3</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-48.79955933118526</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>537</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>537.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>129.5</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>130.52</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>129.29</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>130.52</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>129.29</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>1949.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>4522.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>4522</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>2905.1</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>3384.02</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>3384.02</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>202.4889487032242</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>1949</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>1949.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>130.0</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>130.52</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>129.32</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>130.52</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>129.32</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>1426.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>4513.6</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>4513.6</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>2828.7</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>3384.54</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>3384.54</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>402.955069155837</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>1426</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>1426.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>130.5</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>130.55</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>129.34</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>130.55</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>129.34</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>14304.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>4631.6</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>4631.6</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>3008.0</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>3444.36</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>3444.36</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>730.9797030468612</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>14304</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>14304.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>131.3</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>130.55</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>129.35</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>130.55</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>129.35</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>2020.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>1979.6</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>1979.6</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>1831.1</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>3218.16</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>3218.16</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-206.3058093604918</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>2020</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>2020.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>131.0</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>130.35</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>129.27</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>130.35</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>129.27</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>2911.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>1643.4</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>1643.4</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>1969.1</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>3196.54</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>3196.54</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-221.7741910366926</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>2911</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>2911.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
